--- a/artfynd/A 58960-2025 artfynd.xlsx
+++ b/artfynd/A 58960-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90850714</v>
+        <v>90850715</v>
       </c>
       <c r="B2" t="n">
-        <v>90339</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4787</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539375.0732790802</v>
+        <v>539375</v>
       </c>
       <c r="R2" t="n">
-        <v>7127170.079261337</v>
+        <v>7127160</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>90850716</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +811,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539306.8841489623</v>
+        <v>539307</v>
       </c>
       <c r="R3" t="n">
-        <v>7127090.969053722</v>
+        <v>7127091</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,50 +897,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90850718</v>
+        <v>90850714</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brattberget, Ång</t>
+          <t>Lillslätten-Brattbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540037.9009250327</v>
+        <v>539375</v>
       </c>
       <c r="R4" t="n">
-        <v>7127806.206973564</v>
+        <v>7127170</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,9 +979,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1053,37 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90850715</v>
+        <v>90851099</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539375.2010293911</v>
+        <v>539374</v>
       </c>
       <c r="R5" t="n">
-        <v>7127160.083737466</v>
+        <v>7127157</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,19 +1076,14 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skarp brännande smak. Svag doft påminner om färskt trä/äppelmos.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,50 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90851099</v>
+        <v>90850718</v>
       </c>
       <c r="B6" t="n">
-        <v>90339</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillslätten-Brattbäcken, Ång</t>
+          <t>Brattberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539373.9344863589</v>
+        <v>540038</v>
       </c>
       <c r="R6" t="n">
-        <v>7127157.024931073</v>
+        <v>7127806</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,27 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Skarp brännande smak. Svag doft påminner om färskt trä/äppelmos.</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,9 +1206,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1310,15 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90921641</v>
+        <v>90921638</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539294.1705543089</v>
+        <v>539286</v>
       </c>
       <c r="R7" t="n">
-        <v>7127098.196243093</v>
+        <v>7127078</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,19 +1303,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,15 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90921638</v>
+        <v>90921641</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539286.1576349013</v>
+        <v>539294</v>
       </c>
       <c r="R8" t="n">
-        <v>7127078.099260739</v>
+        <v>7127098</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,19 +1414,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,12 +1460,7 @@
         <v>90921645</v>
       </c>
       <c r="B9" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539429.8743172555</v>
+        <v>539430</v>
       </c>
       <c r="R9" t="n">
-        <v>7127206.856584305</v>
+        <v>7127207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,19 +1525,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,12 +1571,7 @@
         <v>91132758</v>
       </c>
       <c r="B10" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539340.9469956374</v>
+        <v>539341</v>
       </c>
       <c r="R10" t="n">
-        <v>7127150.08360955</v>
+        <v>7127150</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1761,19 +1636,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,15 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91132769</v>
+        <v>91132764</v>
       </c>
       <c r="B11" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539571.9613538829</v>
+        <v>539430</v>
       </c>
       <c r="R11" t="n">
-        <v>7127326.032650577</v>
+        <v>7127208</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1887,21 +1747,11 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1910,6 +1760,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -1935,15 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91132777</v>
+        <v>91132769</v>
       </c>
       <c r="B12" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539306.8841489623</v>
+        <v>539572</v>
       </c>
       <c r="R12" t="n">
-        <v>7127090.969053722</v>
+        <v>7127326</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2008,21 +1858,11 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2031,11 +1871,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -2061,15 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91132780</v>
+        <v>91132777</v>
       </c>
       <c r="B13" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539293.1367002121</v>
+        <v>539307</v>
       </c>
       <c r="R13" t="n">
-        <v>7127076.884248778</v>
+        <v>7127091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2134,19 +1964,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2187,15 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91132764</v>
+        <v>91132780</v>
       </c>
       <c r="B14" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539429.8576309566</v>
+        <v>539293</v>
       </c>
       <c r="R14" t="n">
-        <v>7127208.160330446</v>
+        <v>7127077</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2260,21 +2075,11 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2286,7 +2091,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Möjlig kalkbarrskog</t>
+          <t>Möjlig kalktallskog</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2316,12 +2121,7 @@
         <v>91132781</v>
       </c>
       <c r="B15" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539292.8540203981</v>
+        <v>539293</v>
       </c>
       <c r="R15" t="n">
-        <v>7127099.048788134</v>
+        <v>7127099</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2386,19 +2186,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 58960-2025 artfynd.xlsx
+++ b/artfynd/A 58960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90850715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90850716</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90850714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90851099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90850718</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921638</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921645</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132758</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132764</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132769</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132777</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132780</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,8 +2296,29 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>